--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-priority-extension.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -344,7 +344,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActPriority-cisis</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -686,7 +686,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="39.98046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.1953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-priority-extension.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-priority-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Indique la priorité clinique de l’observation.</t>
+    <t>Extension permettant d’indiquer d'indique la priorité clinique de l’observation.</t>
   </si>
   <si>
     <t>Purpose</t>
